--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_insurance_life.xlsx
@@ -587,47 +587,29 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.134</v>
-      </c>
       <c r="E2">
-        <v>-0.1</v>
-      </c>
-      <c r="G2">
-        <v>0.03274635963427023</v>
-      </c>
-      <c r="H2">
-        <v>0.03274635963427023</v>
-      </c>
-      <c r="I2">
-        <v>0.0317981713511683</v>
-      </c>
-      <c r="J2">
-        <v>0.03055153849706</v>
+        <v>-0.141</v>
       </c>
       <c r="K2">
-        <v>6.77</v>
-      </c>
-      <c r="L2">
-        <v>0.02292583813071453</v>
+        <v>4.37</v>
       </c>
       <c r="M2">
-        <v>8.42</v>
+        <v>7.41</v>
       </c>
       <c r="N2">
-        <v>0.09314159292035397</v>
+        <v>0.1136503067484663</v>
       </c>
       <c r="O2">
-        <v>1.243722304283604</v>
+        <v>1.695652173913043</v>
       </c>
       <c r="P2">
-        <v>8.42</v>
+        <v>7.41</v>
       </c>
       <c r="Q2">
-        <v>0.09314159292035397</v>
+        <v>0.1136503067484663</v>
       </c>
       <c r="R2">
-        <v>1.243722304283604</v>
+        <v>1.695652173913043</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +618,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>78.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V2">
-        <v>0.866150442477876</v>
+        <v>1.098159509202454</v>
       </c>
       <c r="W2">
-        <v>0.2109034267912772</v>
+        <v>0.1281524926686217</v>
       </c>
       <c r="X2">
-        <v>0.06283896266733317</v>
+        <v>0.09695686566705997</v>
       </c>
       <c r="Y2">
-        <v>0.1480644641239441</v>
-      </c>
-      <c r="Z2">
-        <v>-22.38817285822593</v>
-      </c>
-      <c r="AA2">
-        <v>-0.6839931249569234</v>
+        <v>0.03119562700156173</v>
       </c>
       <c r="AB2">
-        <v>0.06147781426469348</v>
-      </c>
-      <c r="AC2">
-        <v>-0.7454709392216169</v>
+        <v>0.0952201351349108</v>
       </c>
       <c r="AD2">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="AG2">
-        <v>-74.56999999999999</v>
+        <v>-68.80999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.03962604908105811</v>
+        <v>0.04103544638917488</v>
       </c>
       <c r="AI2">
-        <v>0.09859899550621201</v>
+        <v>0.09365558912386707</v>
       </c>
       <c r="AJ2">
-        <v>-4.710675931775106</v>
+        <v>19.06094182825492</v>
       </c>
       <c r="AK2">
-        <v>1.842599456387448</v>
+        <v>1.645778521884717</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +666,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.3857290589451913</v>
+        <v>0.45</v>
       </c>
       <c r="AP2">
-        <v>-7.71147880041365</v>
+        <v>-11.09838709677419</v>
       </c>
     </row>
     <row r="3">
@@ -715,47 +688,29 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.134</v>
-      </c>
       <c r="E3">
-        <v>-0.1</v>
-      </c>
-      <c r="G3">
-        <v>0.03274635963427023</v>
-      </c>
-      <c r="H3">
-        <v>0.03274635963427023</v>
-      </c>
-      <c r="I3">
-        <v>0.0317981713511683</v>
-      </c>
-      <c r="J3">
-        <v>0.03055153849706</v>
+        <v>-0.141</v>
       </c>
       <c r="K3">
-        <v>6.77</v>
-      </c>
-      <c r="L3">
-        <v>0.02292583813071453</v>
+        <v>4.37</v>
       </c>
       <c r="M3">
-        <v>8.42</v>
+        <v>7.41</v>
       </c>
       <c r="N3">
-        <v>0.09314159292035397</v>
+        <v>0.1136503067484663</v>
       </c>
       <c r="O3">
-        <v>1.243722304283604</v>
+        <v>1.695652173913043</v>
       </c>
       <c r="P3">
-        <v>8.42</v>
+        <v>7.41</v>
       </c>
       <c r="Q3">
-        <v>0.09314159292035397</v>
+        <v>0.1136503067484663</v>
       </c>
       <c r="R3">
-        <v>1.243722304283604</v>
+        <v>1.695652173913043</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +719,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>78.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V3">
-        <v>0.866150442477876</v>
+        <v>1.098159509202454</v>
       </c>
       <c r="W3">
-        <v>0.2109034267912772</v>
+        <v>0.1281524926686217</v>
       </c>
       <c r="X3">
-        <v>0.06283896266733317</v>
+        <v>0.09695686566705997</v>
       </c>
       <c r="Y3">
-        <v>0.1480644641239441</v>
-      </c>
-      <c r="Z3">
-        <v>-22.38817285822593</v>
-      </c>
-      <c r="AA3">
-        <v>-0.6839931249569234</v>
+        <v>0.03119562700156173</v>
       </c>
       <c r="AB3">
-        <v>0.06147781426469348</v>
-      </c>
-      <c r="AC3">
-        <v>-0.7454709392216169</v>
+        <v>0.0952201351349108</v>
       </c>
       <c r="AD3">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.73</v>
+        <v>2.79</v>
       </c>
       <c r="AG3">
-        <v>-74.56999999999999</v>
+        <v>-68.80999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.03962604908105811</v>
+        <v>0.04103544638917488</v>
       </c>
       <c r="AI3">
-        <v>0.09859899550621201</v>
+        <v>0.09365558912386707</v>
       </c>
       <c r="AJ3">
-        <v>-4.710675931775106</v>
+        <v>19.06094182825492</v>
       </c>
       <c r="AK3">
-        <v>1.842599456387448</v>
+        <v>1.645778521884717</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -821,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.3857290589451913</v>
+        <v>0.45</v>
       </c>
       <c r="AP3">
-        <v>-7.71147880041365</v>
+        <v>-11.09838709677419</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/isle_of_man/isle_of_man_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/isle_of_man/isle_of_man_insurance_life.xlsx
@@ -587,29 +587,47 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0401</v>
+      </c>
       <c r="E2">
-        <v>-0.141</v>
+        <v>-0.0347</v>
+      </c>
+      <c r="G2">
+        <v>0.08900523560209424</v>
+      </c>
+      <c r="H2">
+        <v>0.08900523560209424</v>
+      </c>
+      <c r="I2">
+        <v>0.08097731239092495</v>
+      </c>
+      <c r="J2">
+        <v>0.07823488074461896</v>
       </c>
       <c r="K2">
-        <v>4.37</v>
+        <v>7.24</v>
+      </c>
+      <c r="L2">
+        <v>0.06317626527050611</v>
       </c>
       <c r="M2">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="N2">
-        <v>0.1136503067484663</v>
+        <v>0.0981675392670157</v>
       </c>
       <c r="O2">
-        <v>1.695652173913043</v>
+        <v>1.035911602209945</v>
       </c>
       <c r="P2">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="Q2">
-        <v>0.1136503067484663</v>
+        <v>0.0981675392670157</v>
       </c>
       <c r="R2">
-        <v>1.695652173913043</v>
+        <v>1.035911602209945</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -618,46 +636,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>71.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="V2">
-        <v>1.098159509202454</v>
+        <v>0.8678010471204187</v>
       </c>
       <c r="W2">
-        <v>0.1281524926686217</v>
+        <v>0.2681481481481481</v>
       </c>
       <c r="X2">
-        <v>0.09695686566705997</v>
+        <v>0.08349142961997495</v>
       </c>
       <c r="Y2">
-        <v>0.03119562700156173</v>
+        <v>0.1846567185281732</v>
       </c>
       <c r="AB2">
-        <v>0.0952201351349108</v>
+        <v>0.08241160581844566</v>
       </c>
       <c r="AD2">
-        <v>2.79</v>
+        <v>3.69</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.79</v>
+        <v>3.69</v>
       </c>
       <c r="AG2">
-        <v>-68.80999999999999</v>
+        <v>-62.61</v>
       </c>
       <c r="AH2">
-        <v>0.04103544638917488</v>
+        <v>0.04607316768635285</v>
       </c>
       <c r="AI2">
-        <v>0.09365558912386707</v>
+        <v>0.1175533609429755</v>
       </c>
       <c r="AJ2">
-        <v>19.06094182825492</v>
+        <v>-4.54024655547498</v>
       </c>
       <c r="AK2">
-        <v>1.645778521884717</v>
+        <v>1.793468920080206</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -666,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.45</v>
+        <v>0.361764705882353</v>
       </c>
       <c r="AP2">
-        <v>-11.09838709677419</v>
+        <v>-6.138235294117647</v>
       </c>
     </row>
     <row r="3">
@@ -688,29 +706,47 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0401</v>
+      </c>
       <c r="E3">
-        <v>-0.141</v>
+        <v>-0.0347</v>
+      </c>
+      <c r="G3">
+        <v>0.08900523560209424</v>
+      </c>
+      <c r="H3">
+        <v>0.08900523560209424</v>
+      </c>
+      <c r="I3">
+        <v>0.08097731239092495</v>
+      </c>
+      <c r="J3">
+        <v>0.07823488074461896</v>
       </c>
       <c r="K3">
-        <v>4.37</v>
+        <v>7.24</v>
+      </c>
+      <c r="L3">
+        <v>0.06317626527050611</v>
       </c>
       <c r="M3">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="N3">
-        <v>0.1136503067484663</v>
+        <v>0.0981675392670157</v>
       </c>
       <c r="O3">
-        <v>1.695652173913043</v>
+        <v>1.035911602209945</v>
       </c>
       <c r="P3">
-        <v>7.41</v>
+        <v>7.5</v>
       </c>
       <c r="Q3">
-        <v>0.1136503067484663</v>
+        <v>0.0981675392670157</v>
       </c>
       <c r="R3">
-        <v>1.695652173913043</v>
+        <v>1.035911602209945</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -719,46 +755,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>71.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="V3">
-        <v>1.098159509202454</v>
+        <v>0.8678010471204187</v>
       </c>
       <c r="W3">
-        <v>0.1281524926686217</v>
+        <v>0.2681481481481481</v>
       </c>
       <c r="X3">
-        <v>0.09695686566705997</v>
+        <v>0.08349142961997495</v>
       </c>
       <c r="Y3">
-        <v>0.03119562700156173</v>
+        <v>0.1846567185281732</v>
       </c>
       <c r="AB3">
-        <v>0.0952201351349108</v>
+        <v>0.08241160581844566</v>
       </c>
       <c r="AD3">
-        <v>2.79</v>
+        <v>3.69</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.79</v>
+        <v>3.69</v>
       </c>
       <c r="AG3">
-        <v>-68.80999999999999</v>
+        <v>-62.61</v>
       </c>
       <c r="AH3">
-        <v>0.04103544638917488</v>
+        <v>0.04607316768635285</v>
       </c>
       <c r="AI3">
-        <v>0.09365558912386707</v>
+        <v>0.1175533609429755</v>
       </c>
       <c r="AJ3">
-        <v>19.06094182825492</v>
+        <v>-4.54024655547498</v>
       </c>
       <c r="AK3">
-        <v>1.645778521884717</v>
+        <v>1.793468920080206</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -767,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.45</v>
+        <v>0.361764705882353</v>
       </c>
       <c r="AP3">
-        <v>-11.09838709677419</v>
+        <v>-6.138235294117647</v>
       </c>
     </row>
   </sheetData>
